--- a/master.xlsx
+++ b/master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://philchurchman-my.sharepoint.com/personal/phil_philchurchman_com/Documents/Dev/GitHub/dmdu/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdchu\OneDrive\Documents\Dev\dmdu2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{9EC63814-752C-4CF2-B3CB-F9CED09498D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBC56874-3D13-41B9-831D-09BE5E365325}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F69F5BB4-DFA7-43DA-B43A-FCB2E310159E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Methods" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,12 @@
     <t>Method</t>
   </si>
   <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
     <t>DMDU</t>
   </si>
   <si>
@@ -74,194 +80,13 @@
     <t>Adaptation planning</t>
   </si>
   <si>
+    <t>System adaptation</t>
+  </si>
+  <si>
+    <t>Any suitable</t>
+  </si>
+  <si>
     <t>Assessing vulnerabilities and risks for the purpose of adaptation planning.</t>
-  </si>
-  <si>
-    <t>Agile project management</t>
-  </si>
-  <si>
-    <t>Breaks down large projects into more manageable tasks, which are completed in short iterations throughout the project life cycle.</t>
-  </si>
-  <si>
-    <t>[["(Dong et al., 2024)", "https://doi.org/10.1177/87569728241254095"]]</t>
-  </si>
-  <si>
-    <t>Backcasting</t>
-  </si>
-  <si>
-    <t>Starts with defining a desirable future outcome and works backward to identify the necessary steps to achieve that outcome</t>
-  </si>
-  <si>
-    <t>Dynamic Adaptive Planning</t>
-  </si>
-  <si>
-    <t>Builds flexibility and learning mechanisms into plans that enable continuous adaptation through implementation.</t>
-  </si>
-  <si>
-    <t>Dynamic Adaptive Policy Pathways</t>
-  </si>
-  <si>
-    <t>Builds adaptability into a plan while directing action to a particular goal, placing emphasis on system analysis to identify objectives, constraints and uncertainties.</t>
-  </si>
-  <si>
-    <t>Engineering Options Analysis</t>
-  </si>
-  <si>
-    <t>Assesses the value of building flexibility into an engineering design.</t>
-  </si>
-  <si>
-    <t>Info-gap Decision Theory</t>
-  </si>
-  <si>
-    <t>Prioritises alternatives by considering trade-offs between robustness and optimisation of desired outcomes.</t>
-  </si>
-  <si>
-    <t>Low / no Regret Options</t>
-  </si>
-  <si>
-    <t>Focuses on short term decisions that are robust to most/all foreseeable scenarios.</t>
-  </si>
-  <si>
-    <t>Real Options Analysis</t>
-  </si>
-  <si>
-    <t>Builds flexibility and reversibility into plans assuming uncertainty will reduce over time.</t>
-  </si>
-  <si>
-    <t>Retroductive option assessment</t>
-  </si>
-  <si>
-    <t>Identify the conditions that would need to be true for an option to be viable, then assess the likelihood of each condition being fulfilled.</t>
-  </si>
-  <si>
-    <t>[["(Churchman et al., 2025)", "https://doi.org/10.1016/j.rser.2025.115898"]]</t>
-  </si>
-  <si>
-    <t>Robust Decision Making</t>
-  </si>
-  <si>
-    <t>Uses computation to assess decision options against multiple combinations of input variable assumptions.</t>
-  </si>
-  <si>
-    <t>Scenario planning</t>
-  </si>
-  <si>
-    <t>Considers decision options against pre-defined future scenarios without attempting to assess scenario probability.</t>
-  </si>
-  <si>
-    <t>Vision-led planning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Focuses on what would be required to achieve less car-dependent future mobility.  A response to “predict and provide” approaches that reinforce current mobility solutions.  </t>
-  </si>
-  <si>
-    <t>[["(Hopkinson et al., 2025))", "https://tps.org.uk/public/downloads/zOLlm/Vision-Led%20Planning%20Report.pdf"]]</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>Is option reqt</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Uncertainty will reduce with time / knowledge</t>
-  </si>
-  <si>
-    <t>Uncertain variables are quantifiable</t>
-  </si>
-  <si>
-    <t>Strategic design culture</t>
-  </si>
-  <si>
-    <t>Adaptive change culture</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>Simplicity is important</t>
-  </si>
-  <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>Uncertainty framing</t>
-  </si>
-  <si>
-    <t>Decision robustness</t>
-  </si>
-  <si>
-    <t>Decision optimisation</t>
-  </si>
-  <si>
-    <t>System adaptation</t>
-  </si>
-  <si>
-    <t>Process</t>
-  </si>
-  <si>
-    <t>Computational</t>
-  </si>
-  <si>
-    <t>Any suitable</t>
-  </si>
-  <si>
-    <t>Qualitative</t>
-  </si>
-  <si>
-    <t>[["(Vergragt &amp; Quist, 2011)", "https://www.sciencedirect.com/science/article/pii/S004016251100062X"], ["(Holmberg &amp; Robert, 2011)", "https://doi.org/10.1080/13504500009470049"]]</t>
-  </si>
-  <si>
-    <t>[["(Moret, 2012)", "https://www.fhi360.org/wp-content/uploads/drupal/documents/Vulnerability%20Assessment%20Literature%20Review.pdf"], ["(Birkmann et al., 2010)", "https://doi.org/10.1007/s11625-010-0111-3"], ["(Carter et al.,  2015)", "https://doi.org/10.1016/j.progress.2013.08.001"]]</t>
-  </si>
-  <si>
-    <t>[["(Roelich &amp; Giesekam, 2019)", "https://doi.org/10.1080/14693062.2018.1479238"], ["(Haasnoot, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_4"]]</t>
-  </si>
-  <si>
-    <t>[["(de Neufville &amp; Smet, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_6"], ["(de Neufville et al., 2019)", "https://doi.org/10.1007/978-3-030-05252-2_11"]]</t>
-  </si>
-  <si>
-    <t>[["(Ben-Haim, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_5"]]</t>
-  </si>
-  <si>
-    <t>[["(Dittrich et al., 2016)", "https://doi.org/10.1016/j.ecolecon.2015.12.006"]]</t>
-  </si>
-  <si>
-    <t>[["(Lempert, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_2"]]</t>
-  </si>
-  <si>
-    <t>[["(Shavazipour &amp; Stewart, 2021)", "https://doi.org/10.1007/s12351-019-00512-1"], ["(Amer et al., 2013)", "http://dx.doi.org/10.1016/j.futures.2012.10.003"]]</t>
-  </si>
-  <si>
-    <t>(From ChatGPT) Agile project management is an iterative and flexible approach to managing projects that focuses on delivering value incrementally, responding quickly to change, and continuously improving through collaboration and feedback. Instead of following a fixed, linear plan, Agile breaks work into small, manageable cycles (often called iterations or sprints) where teams plan, build, test, and review outcomes frequently.
-Core characteristics include:
-Iterative development: Work is completed in short cycles with regular reassessment.
-Customer collaboration: Ongoing engagement with stakeholders to ensure the product meets evolving needs.
-Adaptability: Plans evolve as new information, feedback, or changes in context emerge.
-Cross-functional teams: Teams with diverse skills work closely together, often with high autonomy.
-Continuous improvement: Each iteration includes reflection (e.g., retrospectives) to improve processes and quality.</t>
-  </si>
-  <si>
-    <t>(From ChatGPT) Backcasting is a strategic planning method that begins by defining a desirable future state and then works backward to identify the actions, policies, and steps needed to achieve that future from the present. Unlike forecasting—which projects current trends forward—backcasting starts with the end goal and asks: “What must happen between now and then to make this future possible?”
-Key features of backcasting
-Future-oriented: Starts with a vision, target, or scenario (e.g., a carbon-neutral city by 2050).
-Strategic and normative: Focuses on what should happen, not what is most likely to occur.
-Works well under uncertainty: Helps organizations plan when long-term change is complex or unpredictable.</t>
-  </si>
-  <si>
-    <t>[["(Walker et al., 2019)", "https://doi.org/10.1007/978-3-030-05252-2_3"], ["(Wall et al., 2015)", "https://doi.org/10.1061/(ASCE)IS.1943-555X.0000257"]]</t>
-  </si>
-  <si>
-    <t>Protective adaptivity</t>
-  </si>
-  <si>
-    <t>Dynamic adaptivity</t>
   </si>
   <si>
     <t>(From ChatGPT) IPCC Framework for Adaptation Planning: The IPCC describes adaptation planning as an iterative risk-management process. While specific diagrams vary across reports (e.g., AR4, AR5, AR6), the core steps remain consistent. The following reflects the framework widely used in IPCC AR5 and expanded in AR6:
@@ -284,6 +109,73 @@
 Adjust measures over time—reflecting the iterative nature emphasized by the IPCC.</t>
   </si>
   <si>
+    <t>[["(Moret, 2012)", "https://www.fhi360.org/wp-content/uploads/drupal/documents/Vulnerability%20Assessment%20Literature%20Review.pdf"], ["(Birkmann et al., 2010)", "https://doi.org/10.1007/s11625-010-0111-3"], ["(Carter et al.,  2015)", "https://doi.org/10.1016/j.progress.2013.08.001"]]</t>
+  </si>
+  <si>
+    <t>Agile project management</t>
+  </si>
+  <si>
+    <t>Protective adaptivity</t>
+  </si>
+  <si>
+    <t>Qualitative</t>
+  </si>
+  <si>
+    <t>Breaks down large projects into more manageable tasks, which are completed in short iterations throughout the project life cycle.</t>
+  </si>
+  <si>
+    <t>(From ChatGPT) Agile project management is an iterative and flexible approach to managing projects that focuses on delivering value incrementally, responding quickly to change, and continuously improving through collaboration and feedback. Instead of following a fixed, linear plan, Agile breaks work into small, manageable cycles (often called iterations or sprints) where teams plan, build, test, and review outcomes frequently.
+Core characteristics include:
+Iterative development: Work is completed in short cycles with regular reassessment.
+Customer collaboration: Ongoing engagement with stakeholders to ensure the product meets evolving needs.
+Adaptability: Plans evolve as new information, feedback, or changes in context emerge.
+Cross-functional teams: Teams with diverse skills work closely together, often with high autonomy.
+Continuous improvement: Each iteration includes reflection (e.g., retrospectives) to improve processes and quality.</t>
+  </si>
+  <si>
+    <t>[["(Dong et al., 2024)", "https://doi.org/10.1177/87569728241254095"]]</t>
+  </si>
+  <si>
+    <t>Backcasting</t>
+  </si>
+  <si>
+    <t>Uncertainty framing</t>
+  </si>
+  <si>
+    <t>Starts with defining a desirable future outcome and works backward to identify the necessary steps to achieve that outcome</t>
+  </si>
+  <si>
+    <t>(From ChatGPT) Backcasting is a strategic planning method that begins by defining a desirable future state and then works backward to identify the actions, policies, and steps needed to achieve that future from the present. Unlike forecasting—which projects current trends forward—backcasting starts with the end goal and asks: “What must happen between now and then to make this future possible?”
+Key features of backcasting
+Future-oriented: Starts with a vision, target, or scenario (e.g., a carbon-neutral city by 2050).
+Strategic and normative: Focuses on what should happen, not what is most likely to occur.
+Works well under uncertainty: Helps organizations plan when long-term change is complex or unpredictable.</t>
+  </si>
+  <si>
+    <t>[["(Vergragt &amp; Quist, 2011)", "https://www.sciencedirect.com/science/article/pii/S004016251100062X"], ["(Holmberg &amp; Robert, 2011)", "https://doi.org/10.1080/13504500009470049"]]</t>
+  </si>
+  <si>
+    <t>Dynamic Adaptive Planning</t>
+  </si>
+  <si>
+    <t>Builds flexibility and learning mechanisms into plans that enable continuous adaptation through implementation.</t>
+  </si>
+  <si>
+    <t>(Walker et al., 2019) DAP is a DMDU approach for designing a plan that explicitly includes provisions for adaptation as conditions change and knowledge is gained.  The resulting plan combines actions to be taken right away with those that make important commitments to shape the future and those that preserve needed flexibility for the future.  The approach includes the specification of a monitoring system, together with the specification of actions to be taken when specific trigger values are reached.</t>
+  </si>
+  <si>
+    <t>[["(Walker et al., 2019)", "https://doi.org/10.1007/978-3-030-05252-2_3"], ["(Wall et al., 2015)", "https://doi.org/10.1061/(ASCE)IS.1943-555X.0000257"]]</t>
+  </si>
+  <si>
+    <t>Dynamic Adaptive Policy Pathways</t>
+  </si>
+  <si>
+    <t>Dynamic adaptivity</t>
+  </si>
+  <si>
+    <t>Builds adaptability into a plan while directing action to a particular goal, placing emphasis on system analysis to identify objectives, constraints and uncertainties.</t>
+  </si>
+  <si>
     <t>(Haasnoot et al., 2019) Dynamic Adaptive Policy Pathways (DAPP) is a DMDU approach that explicitly includes decision making over time. The essence is proactive and dynamic planning in response to how the future actually unfolds.
 DAPP explores alternative sequences of decisions (adaptation pathways) for multiple futures and illuminates the path dependency of alternative strategies. It opens the decision space and helps to overcome policy paralysis due to deep uncertainty. There are different routes that can achieve the objectives under changing conditions (like ‘different roads leading to Rome’).
 Policy actions have an uncertain design life and might fail sooner or later to continue achieving objectives as the operating conditions change (i.e. they reach an adaptation tipping point (ATP)). Similarly, opportunity tipping points may occur.
@@ -291,10 +183,31 @@
 DAPP supports the design of a dynamic adaptive strategy that includes initial actions, long-term options, and adaptation signals to identify when to implement the long-term options or revisit decisions.</t>
   </si>
   <si>
-    <t>(Walker et al., 2019) DAP is a DMDU approach for designing a plan that explicitly includes provisions for adaptation as conditions change and knowledge is gained.  The resulting plan combines actions to be taken right away with those that make important commitments to shape the future and those that preserve needed flexibility for the future.  The approach includes the specification of a monitoring system, together with the specification of actions to be taken when specific trigger values are reached.</t>
+    <t>[["(Roelich &amp; Giesekam, 2019)", "https://doi.org/10.1080/14693062.2018.1479238"], ["(Haasnoot, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_4"]]</t>
+  </si>
+  <si>
+    <t>Engineering Options Analysis</t>
+  </si>
+  <si>
+    <t>Decision optimisation</t>
+  </si>
+  <si>
+    <t>Computational</t>
+  </si>
+  <si>
+    <t>Assesses the value of building flexibility into an engineering design.</t>
   </si>
   <si>
     <t>(de Neuville &amp; Smet, 2019) Engineering Options Analysis (EOA) refers to the process of assessing the value of including flexibility in the design and management of technical systems. It consists of procedures for calculating the value of options (e.g., the benefits due to flexibility in the timing, size, and location of changes in the engineering system) in terms of the distribution of additional benefits due to the options. EOA presents these benefits to decisionmakers in terms of average expectations, extreme possibilities, and initial capital expenses (Capex). Decisionmakers can choose whether (or to what extent) to monetize these values.</t>
+  </si>
+  <si>
+    <t>[["(de Neufville &amp; Smet, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_6"], ["(de Neufville et al., 2019)", "https://doi.org/10.1007/978-3-030-05252-2_11"]]</t>
+  </si>
+  <si>
+    <t>Info-gap Decision Theory</t>
+  </si>
+  <si>
+    <t>Prioritises alternatives by considering trade-offs between robustness and optimisation of desired outcomes.</t>
   </si>
   <si>
     <t>(Ben-Haim, 2019) Info-Gap (IG) Decision Theory is a method for prioritizing alternatives and making choices and decisions under deep uncertainty.
@@ -311,6 +224,15 @@
 Two examples of info-gap analysis are presented, one quantitative that uses mathematics and one qualitative that uses only verbal analysis.</t>
   </si>
   <si>
+    <t>[["(Ben-Haim, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_5"]]</t>
+  </si>
+  <si>
+    <t>Low / no Regret Options</t>
+  </si>
+  <si>
+    <t>Focuses on short term decisions that are robust to most/all foreseeable scenarios.</t>
+  </si>
+  <si>
     <t>(From ChatGPT) Low-regrets options planning is a decision-making approach that prioritizes actions that yield net benefits across multiple plausible futures, minimizing the risk of wasted investment even if conditions change or impacts are less severe than expected.
 Key characteristics:
 Robust across scenarios: Works well whether future changes are moderate or severe.
@@ -320,7 +242,13 @@
 Suitable for uncertainty: Common in climate adaptation planning where exact impacts are hard to predict.</t>
   </si>
   <si>
-    <t>[["(Dittrich et al., 2016)", "https://doi.org/10.1016/j.ecolecon.2015.12.006"], ["(Borison, 2005)", "https://doi.org/10.1111/j.1745-6622.2005.00029.x"], ["(Trigeogis &amp; Reuer, 2017)", "https://doi.org/10.1002%2Fsmj.2593"], ["(Bowman &amp; Moskowitz, 2001)", "https://doi.org/10.1287/orsc.12.6.772.10080"]]</t>
+    <t>[["(Dittrich et al., 2016)", "https://doi.org/10.1016/j.ecolecon.2015.12.006"]]</t>
+  </si>
+  <si>
+    <t>Real Options Analysis</t>
+  </si>
+  <si>
+    <t>Builds flexibility and reversibility into plans assuming uncertainty will reduce over time.</t>
   </si>
   <si>
     <t>(From ChatGPT) Real Options Analysis is a framework for evaluating investment opportunities that explicitly accounts for uncertainty and managerial flexibility, by treating strategic decisions as “options” that can be exercised in the future when more information is known, thereby enhancing decision-making under risk.
@@ -335,13 +263,43 @@
 Investing in adaptive climate solutions with adjustable scale.</t>
   </si>
   <si>
+    <t>[["(Dittrich et al., 2016)", "https://doi.org/10.1016/j.ecolecon.2015.12.006"], ["(Borison, 2005)", "https://doi.org/10.1111/j.1745-6622.2005.00029.x"], ["(Trigeogis &amp; Reuer, 2017)", "https://doi.org/10.1002%2Fsmj.2593"], ["(Bowman &amp; Moskowitz, 2001)", "https://doi.org/10.1287/orsc.12.6.772.10080"]]</t>
+  </si>
+  <si>
+    <t>Retroductive option assessment</t>
+  </si>
+  <si>
+    <t>Decision robustness</t>
+  </si>
+  <si>
+    <t>Identify the conditions that would need to be true for an option to be viable, then assess the likelihood of each condition being fulfilled.</t>
+  </si>
+  <si>
     <t xml:space="preserve">(Churchman et al., 2025) The significance of adopting a realist ontology is that, unlike relativist ontology, it assumes that reality and truth are independent of context and the individual values, norms and beliefs of humans.  Retroduction is a methodological alternative to more commonly used deductive and inductive research methods. The “retro” in retroduction implies a form of backcasting in which analysis considers a predefined theory, in this case that a certain energy source option could be feasible; identifies the conditions under which this theory would be true; and assesses the likelihood of these conditions being met.  It is aligned with answer first / pyramid principle approaches used by strategy consultancies to assess strategic options.
 </t>
+  </si>
+  <si>
+    <t>[["(Churchman et al., 2025)", "https://doi.org/10.1016/j.rser.2025.115898"]]</t>
+  </si>
+  <si>
+    <t>Robust Decision Making</t>
+  </si>
+  <si>
+    <t>Uses computation to assess decision options against multiple combinations of input variable assumptions.</t>
   </si>
   <si>
     <t>(Lempert, 2019) Robust Decision Making (RDM) is a set of concepts, processes, and enabling tools that use computation, not to make better predictions, but to yield better decisions under conditions of deep uncertainty.
 RDM combines Decision Analysis, Assumption-Based Planning, scenarios, and Exploratory Modeling to stress test strategies over myriad plausible paths into the future, and then to identify policy-relevant scenarios and robust adaptive strategies.
 RDM embeds analytic tools in a decision support process called “deliberation with analysis” that promotes learning and consensus-building among stakeholders.</t>
+  </si>
+  <si>
+    <t>[["(Lempert, 2019)", "https://doi.org/10.1007/978-3-030-05252-2_2"]]</t>
+  </si>
+  <si>
+    <t>Scenario planning</t>
+  </si>
+  <si>
+    <t>Considers decision options against pre-defined future scenarios without attempting to assess scenario probability.</t>
   </si>
   <si>
     <t>(From ChatGPT) Scenario planning is a structured approach to long-term planning that constructs a set of plausible, contrasting future scenarios based on key drivers of change and uncertainties, enabling organizations or policymakers to identify robust strategies, anticipate risks, and make flexible, informed decisions.
@@ -353,14 +311,56 @@
 Iterative process: Scenarios are updated as conditions, knowledge, or objectives change.</t>
   </si>
   <si>
+    <t>[["(Shavazipour &amp; Stewart, 2021)", "https://doi.org/10.1007/s12351-019-00512-1"], ["(Amer et al., 2013)", "http://dx.doi.org/10.1016/j.futures.2012.10.003"]]</t>
+  </si>
+  <si>
+    <t>Vision-led planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focuses on what would be required to achieve less car-dependent future mobility.  A response to “predict and provide” approaches that reinforce current mobility solutions.  </t>
+  </si>
+  <si>
     <t xml:space="preserve">(Hopkinson et al, 2025)We need a new approach to address congestion; improve road safety; and facilitate new developments that offer better, sustainable and cost-effective travel options.  This new approach can deliver economic prosperity, healthier communities and improved local environments. In addition, many of these alternative options may be quicker and cheaper to deliver than large-scale road schemes that take time to develop. We also need a more rounded set of objectives for transport planning. A narrow focus on traditional forms of economic growth tends to perpetuate a focus on the needs of certain demographics, namely ‘white collar’ people of working age. These essentially represent a minority but receive most of the emphasis in planning new developments and infrastructure. As a result, the needs of children, students, the elderly, stay-at-home parents, and those with fewer socio-economic opportunities (all of whom positively contribute to the economy) are not catered for by transport investment. We need a fairer transport system. </t>
+  </si>
+  <si>
+    <t>[["(Hopkinson et al., 2025))", "https://tps.org.uk/public/downloads/zOLlm/Vision-Led%20Planning%20Report.pdf"]]</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Is option reqt</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Uncertainty will reduce with time / knowledge</t>
+  </si>
+  <si>
+    <t>Uncertain variables are quantifiable</t>
+  </si>
+  <si>
+    <t>Strategic design culture</t>
+  </si>
+  <si>
+    <t>Adaptive change culture</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>Simplicity is important</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,12 +372,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -415,12 +409,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -438,10 +429,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -730,92 +717,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R14"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="20.69140625" customWidth="1"/>
-    <col min="2" max="2" width="15.61328125" customWidth="1"/>
-    <col min="3" max="3" width="13.4609375" customWidth="1"/>
-    <col min="6" max="6" width="28.4609375" customWidth="1"/>
-    <col min="7" max="7" width="94.3046875" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -851,27 +831,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -907,27 +887,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -939,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -963,27 +943,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -995,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L5">
         <v>50</v>
@@ -1019,27 +999,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -1051,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -1075,27 +1055,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="G7" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -1110,7 +1090,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -1131,27 +1111,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -1166,7 +1146,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1187,27 +1167,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -1243,27 +1223,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -1278,7 +1258,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -1299,27 +1279,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -1355,24 +1335,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
         <v>70</v>
@@ -1411,27 +1391,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -1443,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1467,27 +1447,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="F14" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -1499,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1525,38 +1505,34 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="12.69140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="C2" t="b">
         <v>1</v>
@@ -1565,12 +1541,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -1579,12 +1555,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C4" t="b">
         <v>1</v>
@@ -1593,12 +1569,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="C5" t="b">
         <v>1</v>
@@ -1607,12 +1583,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
@@ -1621,12 +1597,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
@@ -1635,12 +1611,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
@@ -1649,12 +1625,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
@@ -1663,12 +1639,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C10" t="b">
         <v>1</v>
@@ -1677,12 +1653,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C11" t="b">
         <v>1</v>

--- a/master.xlsx
+++ b/master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdchu\OneDrive\Documents\Dev\dmdu2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://philchurchman-my.sharepoint.com/personal/phil_philchurchman_com/Documents/Dev/GitHub/dmdu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F69F5BB4-DFA7-43DA-B43A-FCB2E310159E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6683DC31-10C6-442E-9879-ED2F0E6B4829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1670,4 +1670,318 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010031A138CE6FA91F49A0A97874A235EA8C" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="97b8cd84c0bbe87d685ca82c953a455b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="200c8dbf-7213-4a09-a794-6c3dbc798051" xmlns:ns4="42a51b97-546f-4f13-892e-ab94fc713188" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0b49abd66a1b220b4ad705613e2efec5" ns3:_="" ns4:_="">
+    <xsd:import namespace="200c8dbf-7213-4a09-a794-6c3dbc798051"/>
+    <xsd:import namespace="42a51b97-546f-4f13-892e-ab94fc713188"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:SharingHintHash" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns4:_activity" minOccurs="0"/>
+                <xsd:element ref="ns4:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="200c8dbf-7213-4a09-a794-6c3dbc798051" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SharingHintHash" ma:index="10" nillable="true" ma:displayName="Sharing Hint Hash" ma:description="" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="42a51b97-546f-4f13-892e-ab94fc713188" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="12" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="18" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="19" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="22" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="24" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="25" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="42a51b97-546f-4f13-892e-ab94fc713188" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{108252D5-0DC3-4884-A5AA-CCB3FB3712D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="200c8dbf-7213-4a09-a794-6c3dbc798051"/>
+    <ds:schemaRef ds:uri="42a51b97-546f-4f13-892e-ab94fc713188"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63B93DD1-4BF3-451C-8762-F79A053C5596}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC6AAC9E-4D8D-4305-8B07-7B616164166A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="200c8dbf-7213-4a09-a794-6c3dbc798051"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="42a51b97-546f-4f13-892e-ab94fc713188"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>